--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.145930868920463</v>
+        <v>1.323713766199575</v>
       </c>
       <c r="D2" t="n">
-        <v>10.89841498529742</v>
+        <v>1.770992435110831</v>
       </c>
       <c r="E2" t="n">
-        <v>4.309521297059943</v>
+        <v>0.7002972107722408</v>
       </c>
       <c r="F2" t="n">
-        <v>6.492790978963058</v>
+        <v>1.055078534081497</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.797705815523974</v>
+        <v>0.9421271950226459</v>
       </c>
       <c r="D3" t="n">
-        <v>5.044960138753709</v>
+        <v>0.8198060225474777</v>
       </c>
       <c r="E3" t="n">
-        <v>4.309521297059943</v>
+        <v>0.7002972107722408</v>
       </c>
       <c r="F3" t="n">
-        <v>6.492790978963058</v>
+        <v>1.055078534081497</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.014975163406483</v>
+        <v>1.139933464053553</v>
       </c>
       <c r="D4" t="n">
-        <v>17.61011383236275</v>
+        <v>2.861643497758947</v>
       </c>
       <c r="E4" t="n">
-        <v>4.309521297059943</v>
+        <v>0.7002972107722408</v>
       </c>
       <c r="F4" t="n">
-        <v>6.492790978963058</v>
+        <v>1.055078534081497</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9444454164766108</v>
+        <v>0.1534723801774493</v>
       </c>
       <c r="D5" t="n">
-        <v>24.13832477827083</v>
+        <v>3.92247777646901</v>
       </c>
       <c r="E5" t="n">
-        <v>4.309521297059943</v>
+        <v>0.7002972107722408</v>
       </c>
       <c r="F5" t="n">
-        <v>6.492790978963058</v>
+        <v>1.055078534081497</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.517473084276956</v>
+        <v>1.546589376195005</v>
       </c>
       <c r="D6" t="n">
-        <v>9.743158365718964</v>
+        <v>1.583263234429332</v>
       </c>
       <c r="E6" t="n">
-        <v>4.309521297059943</v>
+        <v>0.7002972107722408</v>
       </c>
       <c r="F6" t="n">
-        <v>6.492790978963058</v>
+        <v>1.055078534081497</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.904348735086687</v>
+        <v>1.609456669451587</v>
       </c>
       <c r="D7" t="n">
-        <v>25.5</v>
+        <v>4.14375</v>
       </c>
       <c r="E7" t="n">
-        <v>4.309521297059943</v>
+        <v>0.7002972107722408</v>
       </c>
       <c r="F7" t="n">
-        <v>6.492790978963058</v>
+        <v>1.055078534081497</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.41947016328038</v>
+        <v>2.018163901533061</v>
       </c>
       <c r="D8" t="n">
-        <v>12.41947016328038</v>
+        <v>2.018163901533061</v>
       </c>
       <c r="E8" t="n">
-        <v>4.309521297059943</v>
+        <v>0.7002972107722408</v>
       </c>
       <c r="F8" t="n">
-        <v>6.492790978963058</v>
+        <v>1.055078534081497</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.85266083089365</v>
+        <v>2.738557385020219</v>
       </c>
       <c r="D9" t="n">
-        <v>10.46659537803745</v>
+        <v>1.700821748931085</v>
       </c>
       <c r="E9" t="n">
-        <v>4.309521297059943</v>
+        <v>0.7002972107722408</v>
       </c>
       <c r="F9" t="n">
-        <v>6.492790978963058</v>
+        <v>1.055078534081497</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4.98059666204508</v>
+        <v>0.8093469575823256</v>
       </c>
       <c r="D10" t="n">
-        <v>17.87293696982465</v>
+        <v>2.904352257596506</v>
       </c>
       <c r="E10" t="n">
-        <v>4.309521297059943</v>
+        <v>0.7002972107722408</v>
       </c>
       <c r="F10" t="n">
-        <v>6.492790978963058</v>
+        <v>1.055078534081497</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
